--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486380_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486380_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7003</v>
+        <v>4.4809</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1011</v>
+        <v>4.344</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5993000000000001</v>
+        <v>0.1369</v>
       </c>
       <c r="G2" t="n">
         <v>1.8561</v>
@@ -610,13 +610,13 @@
         <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3583</v>
+        <v>1.1389</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3073</v>
+        <v>1.5502</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0511</v>
+        <v>-0.4113</v>
       </c>
       <c r="V2" t="n">
         <v>1.921</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H. LOPEZ BARRANTES</t>
+          <t>O. SILVERIO GRULLON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3927</v>
+        <v>4.0592</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3898</v>
+        <v>4.4077</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9971</v>
+        <v>-0.3485</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1206</v>
+        <v>2.8024</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7328</v>
+        <v>0.7114</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8534</v>
+        <v>2.091</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2842</v>
+        <v>3.5756</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0547</v>
+        <v>0.5506</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2295</v>
+        <v>3.0249</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4049</v>
+        <v>-0.7732</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6781</v>
+        <v>0.1608</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0829</v>
+        <v>-0.9339</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>4.1346</v>
+        <v>0.0955</v>
       </c>
       <c r="T3" t="n">
-        <v>4.1278</v>
+        <v>0.6369</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0067</v>
+        <v>-0.5414</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2737</v>
+        <v>-0.1438</v>
       </c>
       <c r="W3" t="n">
         <v>0.1952</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.469</v>
+        <v>-0.339</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. SILVERIO GRULLON</t>
+          <t>S. SALIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5628</v>
+        <v>3.1876</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9729</v>
+        <v>2.3501</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4101</v>
+        <v>0.8374</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8024</v>
+        <v>2.9701</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7114</v>
+        <v>-0.3712</v>
       </c>
       <c r="I4" t="n">
-        <v>2.091</v>
+        <v>3.3413</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5756</v>
+        <v>2.4459</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5506</v>
+        <v>-0.6173</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0249</v>
+        <v>3.0632</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7732</v>
+        <v>0.5242</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1608</v>
+        <v>0.2461</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9339</v>
+        <v>0.2781</v>
       </c>
       <c r="P4" t="n">
-        <v>1.305</v>
+        <v>-0.435</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R4" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4009</v>
+        <v>-0.313</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7979000000000001</v>
+        <v>0.0793</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.603</v>
+        <v>-0.3924</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1438</v>
+        <v>0.9655</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.339</v>
+        <v>-0.1645</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. SALIN</t>
+          <t>T. MC GREW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3205</v>
+        <v>2.5679</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7913</v>
+        <v>2.4126</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5292</v>
+        <v>0.1553</v>
       </c>
       <c r="G5" t="n">
-        <v>2.9701</v>
+        <v>1.3018</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3712</v>
+        <v>0.6659</v>
       </c>
       <c r="I5" t="n">
-        <v>3.3413</v>
+        <v>0.6359</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4459</v>
+        <v>1.3896</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6173</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>3.0632</v>
+        <v>0.4224</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5242</v>
+        <v>-0.0878</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2461</v>
+        <v>-0.3013</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2781</v>
+        <v>0.2136</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.435</v>
+        <v>0.435</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1801</v>
+        <v>-0.1036</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4795</v>
+        <v>-0.1069</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7006</v>
+        <v>0.0033</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9655</v>
+        <v>0.9347</v>
       </c>
       <c r="W5" t="n">
         <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1645</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. MC GREW</t>
+          <t>J. GRANGER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1766</v>
+        <v>1.5809</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0521</v>
+        <v>2.3682</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1245</v>
+        <v>-0.7873</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3018</v>
+        <v>2.7337</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6659</v>
+        <v>0.8515</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6359</v>
+        <v>1.8822</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3896</v>
+        <v>3.1754</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9553</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4224</v>
+        <v>2.2201</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0878</v>
+        <v>-0.4417</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3013</v>
+        <v>-0.1038</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2136</v>
+        <v>-0.3379</v>
       </c>
       <c r="P6" t="n">
-        <v>0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R6" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.495</v>
+        <v>0.4684</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4675</v>
+        <v>0.8676</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0275</v>
+        <v>-0.3993</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9347</v>
+        <v>-1.8387</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>-0.3698</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1952</v>
+        <v>-1.469</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GONZÁLEZ PÉREZ</t>
+          <t>L. GIOVANNETTI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1157</v>
+        <v>1.1121</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4289</v>
+        <v>1.3549</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3132</v>
+        <v>-0.2428</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4408</v>
+        <v>2.5641</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7603</v>
+        <v>1.5936</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6805</v>
+        <v>0.9706</v>
       </c>
       <c r="J7" t="n">
-        <v>1.629</v>
+        <v>2.3379</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8641</v>
+        <v>1.4964</v>
       </c>
       <c r="L7" t="n">
-        <v>0.765</v>
+        <v>0.8415</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1882</v>
+        <v>0.2262</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1038</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.08450000000000001</v>
+        <v>0.1291</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.5225</v>
+        <v>-0.435</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1751</v>
+        <v>-1.305</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>1.7624</v>
+        <v>0.113</v>
       </c>
       <c r="T7" t="n">
-        <v>1.7797</v>
+        <v>0.3221</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0173</v>
+        <v>-0.2091</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.13</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.7602</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. GIOVANNETTI</t>
+          <t>H. LOPEZ BARRANTES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.8108</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9079</v>
+        <v>1.9311</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3661</v>
+        <v>-1.1204</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5641</v>
+        <v>-0.1206</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5936</v>
+        <v>0.7328</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9706</v>
+        <v>-0.8534</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3379</v>
+        <v>0.2842</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4964</v>
+        <v>0.0547</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8415</v>
+        <v>0.2295</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2262</v>
+        <v>-0.4049</v>
       </c>
       <c r="N8" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.6781</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1291</v>
+        <v>-1.0829</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="R8" t="n">
         <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4574</v>
+        <v>1.5526</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.125</v>
+        <v>1.6692</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3324</v>
+        <v>-0.1166</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.13</v>
+        <v>-1.2737</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.13</v>
+        <v>-1.469</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. GRANGER</t>
+          <t>A. GONZÁLEZ PÉREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.364</v>
+        <v>0.0118</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1821</v>
+        <v>0.4483</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8182</v>
+        <v>-0.4365</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7337</v>
+        <v>1.4408</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8515</v>
+        <v>0.7603</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8822</v>
+        <v>0.6805</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1754</v>
+        <v>1.629</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9553</v>
+        <v>0.8641</v>
       </c>
       <c r="L9" t="n">
-        <v>2.2201</v>
+        <v>0.765</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4417</v>
+        <v>-0.1882</v>
       </c>
       <c r="N9" t="n">
         <v>-0.1038</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3379</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2175</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.305</v>
+        <v>-2.1751</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7485000000000001</v>
+        <v>0.6585</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3184</v>
+        <v>0.7991</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4301</v>
+        <v>-0.1406</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.8387</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3698</v>
+        <v>0.1952</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.469</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5221</v>
+        <v>-0.8581</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2576</v>
+        <v>0.7984</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7798</v>
+        <v>-1.6565</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1852</v>
@@ -1234,13 +1234,13 @@
         <v>1.305</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3168</v>
+        <v>0.3473</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1406</v>
+        <v>0.6814</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4574</v>
+        <v>-0.3341</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3252</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.81</v>
+        <v>-2.1027</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7349</v>
+        <v>-1.1508</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0751</v>
+        <v>-0.9518</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2707</v>
@@ -1312,13 +1312,13 @@
         <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0618</v>
+        <v>-0.3545</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.1009</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3769</v>
+        <v>-0.2536</v>
       </c>
       <c r="V11" t="n">
         <v>-1.13</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9499</v>
+        <v>-2.9306</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4074</v>
+        <v>-1.2956</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5426</v>
+        <v>-1.635</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1078</v>
@@ -1390,13 +1390,13 @@
         <v>0.435</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0172</v>
+        <v>0.0021</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.0433</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0513</v>
+        <v>-0.0412</v>
       </c>
       <c r="V12" t="n">
         <v>-2.2599</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.8924</v>
+        <v>11.9198</v>
       </c>
       <c r="E13" t="n">
-        <v>16.9414</v>
+        <v>17.9689</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.0492</v>
+        <v>-6.049200000000001</v>
       </c>
       <c r="G13" t="n">
         <v>11.9847</v>
@@ -1444,7 +1444,7 @@
         <v>15.297</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6785</v>
+        <v>2.678500000000001</v>
       </c>
       <c r="L13" t="n">
         <v>12.6185</v>
@@ -1468,19 +1468,19 @@
         <v>10.8751</v>
       </c>
       <c r="S13" t="n">
-        <v>2.577599999999999</v>
+        <v>3.6052</v>
       </c>
       <c r="T13" t="n">
-        <v>5.413600000000001</v>
+        <v>6.441300000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.8361</v>
+        <v>-2.8363</v>
       </c>
       <c r="V13" t="n">
         <v>-5.8451</v>
       </c>
       <c r="W13" t="n">
-        <v>4.931</v>
+        <v>4.930999999999999</v>
       </c>
       <c r="X13" t="n">
         <v>-10.7762</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5483</v>
+        <v>6.8752</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0857</v>
+        <v>4.868</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4626</v>
+        <v>2.0073</v>
       </c>
       <c r="G14" t="n">
         <v>3.8038</v>
@@ -1546,13 +1546,13 @@
         <v>1.305</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4507</v>
+        <v>-0.1238</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.1094</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.2331</v>
       </c>
       <c r="V14" t="n">
         <v>1.8902</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4709</v>
+        <v>1.5095</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4357</v>
+        <v>2.6592</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9648</v>
+        <v>-1.1498</v>
       </c>
       <c r="G15" t="n">
         <v>-0.6885</v>
@@ -1624,13 +1624,13 @@
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1387</v>
+        <v>0.1772</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2896</v>
+        <v>0.5131</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1509</v>
+        <v>-0.3359</v>
       </c>
       <c r="V15" t="n">
         <v>1.1507</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. MARTINEZ CLARIANA</t>
+          <t>J. VAN ZEGEREN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.043</v>
+        <v>0.0912</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5904</v>
+        <v>0.0324</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5474</v>
+        <v>0.0588</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.6522</v>
+        <v>-0.5485</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.1405</v>
+        <v>-0.4743</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.5117</v>
+        <v>-0.0741</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.283</v>
+        <v>-0.6057</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7236</v>
+        <v>-0.7205</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4407</v>
+        <v>0.1147</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.3692</v>
+        <v>0.0573</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4169</v>
+        <v>0.2461</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.9523</v>
+        <v>-0.1889</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7626</v>
+        <v>-0.0352</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5933</v>
+        <v>0.6381</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1693</v>
+        <v>-0.6733</v>
       </c>
       <c r="V16" t="n">
-        <v>2.4552</v>
+        <v>-0.1952</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4552</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. VAN ZEGEREN</t>
+          <t>J. ROUND</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0032</v>
+        <v>0.0786</v>
       </c>
       <c r="E17" t="n">
-        <v>1.15</v>
+        <v>1.3101</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1467</v>
+        <v>-1.2316</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5485</v>
+        <v>0.6049</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4743</v>
+        <v>0.6751</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0741</v>
+        <v>-0.0701</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6057</v>
+        <v>1.8912</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7205</v>
+        <v>1.241</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1147</v>
+        <v>0.6502</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0573</v>
+        <v>-1.2863</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2461</v>
+        <v>-0.5659</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1889</v>
+        <v>-0.7204</v>
       </c>
       <c r="P17" t="n">
-        <v>0.87</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q17" t="n">
+        <v>-2.1751</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.4813</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.1009</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.3803</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.695</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.695</v>
+      </c>
+      <c r="X17" t="n">
         <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.8769</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.7557</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-0.8788</v>
-      </c>
-      <c r="V17" t="n">
-        <v>-0.1952</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-0.1952</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.666</v>
+        <v>-0.1946</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3461</v>
+        <v>0.4579</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0121</v>
+        <v>-0.6525</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6331</v>
@@ -1858,13 +1858,13 @@
         <v>1.305</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.99</v>
+        <v>-0.5185</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1286</v>
+        <v>0.2403</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1185</v>
+        <v>-0.7589</v>
       </c>
       <c r="V18" t="n">
         <v>0.7395</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. ROUND</t>
+          <t>A. MARTINEZ CLARIANA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7281</v>
+        <v>-0.7489</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8631</v>
+        <v>1.1376</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5913</v>
+        <v>-1.8864</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6049</v>
+        <v>-2.6522</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6751</v>
+        <v>-1.1405</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0701</v>
+        <v>-1.5117</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8912</v>
+        <v>-0.283</v>
       </c>
       <c r="K19" t="n">
-        <v>1.241</v>
+        <v>-0.7236</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6502</v>
+        <v>0.4407</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2863</v>
+        <v>-2.3692</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5659</v>
+        <v>-0.4169</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7204</v>
+        <v>-1.9523</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.7401</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q19" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R19" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.288</v>
+        <v>0.9707</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.548</v>
+        <v>1.1404</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.74</v>
+        <v>-0.1698</v>
       </c>
       <c r="V19" t="n">
-        <v>1.695</v>
+        <v>2.4552</v>
       </c>
       <c r="W19" t="n">
-        <v>1.695</v>
+        <v>2.4552</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.814</v>
+        <v>-2.5885</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2272</v>
+        <v>-0.3316</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0411</v>
+        <v>-2.2569</v>
       </c>
       <c r="G20" t="n">
         <v>-1.5071</v>
@@ -2014,13 +2014,13 @@
         <v>0.6525</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1732</v>
+        <v>0.3987</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.4074</v>
       </c>
       <c r="U20" t="n">
-        <v>0.207</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>1.13</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1912</v>
+        <v>-2.6761</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.467</v>
+        <v>-0.1317</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7243</v>
+        <v>-2.5444</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8028</v>
@@ -2092,13 +2092,13 @@
         <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9985000000000001</v>
+        <v>-0.4834</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6165</v>
+        <v>-0.2812</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.382</v>
+        <v>-0.2022</v>
       </c>
       <c r="V21" t="n">
         <v>-2.2599</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.6221</v>
+        <v>-4.8103</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4307</v>
+        <v>0.0163</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.1914</v>
+        <v>-4.8266</v>
       </c>
       <c r="G22" t="n">
         <v>-3.6714</v>
@@ -2170,13 +2170,13 @@
         <v>0.435</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2982</v>
+        <v>-0.4864</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4675</v>
+        <v>-0.0204</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8307</v>
+        <v>-0.466</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.9363</v>
+        <v>-6.9382</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.7512</v>
+        <v>-3.9689</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.1851</v>
+        <v>-2.9693</v>
       </c>
       <c r="G23" t="n">
         <v>-5.8899</v>
@@ -2248,13 +2248,13 @@
         <v>1.305</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5037</v>
+        <v>-0.5056</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5924</v>
+        <v>0.1899</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9113</v>
+        <v>-0.6955</v>
       </c>
       <c r="V23" t="n">
         <v>-0.7602</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.8923</v>
+        <v>-9.402099999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>6.0493</v>
+        <v>6.049299999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-16.9416</v>
+        <v>-15.4514</v>
       </c>
       <c r="G24" t="n">
         <v>-11.9848</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.3905</v>
+        <v>-3.390500000000001</v>
       </c>
       <c r="I24" t="n">
         <v>-8.594100000000001</v>
@@ -2326,13 +2326,13 @@
         <v>8.699999999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.5777</v>
+        <v>-1.0876</v>
       </c>
       <c r="T24" t="n">
         <v>2.8361</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.4136</v>
+        <v>-3.9237</v>
       </c>
       <c r="V24" t="n">
         <v>5.8453</v>
